--- a/Plannings 2026 S45.xlsx
+++ b/Plannings 2026 S45.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6EA6F87-D711-4845-B2D1-D0C97DB6B237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{B6EA6F87-D711-4845-B2D1-D0C97DB6B237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C51DBFB-A618-4CBC-AB0E-D5924D7F5B62}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="128">
   <si>
     <t>Planning des salariés du 02/11/2026 au 08/11/2026</t>
   </si>
@@ -75,9 +75,6 @@
     <t>13:45/17:45</t>
   </si>
   <si>
-    <t>17:45/22:30</t>
-  </si>
-  <si>
     <t>BONNET Mateo</t>
   </si>
   <si>
@@ -327,9 +324,6 @@
     <t>13:30/19:30</t>
   </si>
   <si>
-    <t>19:30/21:30</t>
-  </si>
-  <si>
     <t>SANGARNE Enzo</t>
   </si>
   <si>
@@ -409,6 +403,9 @@
   </si>
   <si>
     <t>EDF // C. PADEL // LEAGUES // LDC</t>
+  </si>
+  <si>
+    <t>17:45/21:30</t>
   </si>
 </sst>
 </file>
@@ -822,22 +819,7 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -849,13 +831,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -868,15 +844,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -955,6 +922,36 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5234,98 +5231,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="G3" s="16" t="s">
+      <c r="E3" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="F3" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H3" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="H4" s="13" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="20" t="s">
+      <c r="B5" s="14"/>
+      <c r="C5" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="20"/>
-      <c r="G5" s="36" t="s">
+      <c r="F5" s="15"/>
+      <c r="G5" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="21"/>
+      <c r="H5" s="16"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="22"/>
+      <c r="A6" s="52"/>
       <c r="B6" s="1"/>
       <c r="C6" s="2" t="s">
         <v>14</v>
@@ -5337,13 +5334,13 @@
         <v>15</v>
       </c>
       <c r="F6" s="2"/>
-      <c r="G6" s="37" t="s">
+      <c r="G6" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="23"/>
+      <c r="H6" s="17"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="22"/>
+      <c r="A7" s="52"/>
       <c r="B7" s="1"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -5352,1044 +5349,1044 @@
       <c r="G7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="23"/>
+      <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="24"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26" t="s">
+      <c r="A8" s="53"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="H8" s="20"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="27"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="44" t="s">
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="16"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="53"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="21"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="24"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="46" t="s">
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="27"/>
+      <c r="H10" s="20"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="16"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="53"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20" t="s">
+      <c r="D12" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="20"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="48"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="50"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="C14" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="D14" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="21"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="24"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="27"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="29"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="31"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
+      <c r="F14" s="15"/>
+      <c r="G14" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="H14" s="16"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="52"/>
+      <c r="B15" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="44" t="s">
-        <v>121</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="20"/>
-      <c r="G14" s="44" t="s">
-        <v>121</v>
-      </c>
-      <c r="H14" s="21"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="22"/>
-      <c r="B15" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="45" t="s">
-        <v>120</v>
+      <c r="D15" s="35" t="s">
+        <v>118</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="H15" s="23"/>
+      <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="22"/>
+      <c r="A16" s="52"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
-      <c r="D16" s="45"/>
+      <c r="D16" s="35"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H16" s="23"/>
+      <c r="H16" s="17"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="22"/>
+      <c r="A17" s="52"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
-      <c r="D17" s="45"/>
+      <c r="D17" s="35"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H17" s="23"/>
+        <v>31</v>
+      </c>
+      <c r="H17" s="17"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="22"/>
+      <c r="A18" s="52"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="45"/>
+      <c r="D18" s="35"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="H18" s="23"/>
+      <c r="G18" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="H18" s="17"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="24"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="43" t="s">
+      <c r="A19" s="53"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" s="20"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="H19" s="27"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
+      <c r="B20" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="15"/>
+      <c r="H20" s="16"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="53"/>
+      <c r="B21" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="G21" s="19"/>
+      <c r="H21" s="20"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="15"/>
+      <c r="F22" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="15"/>
+      <c r="H22" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="20"/>
-      <c r="H20" s="21"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="24"/>
-      <c r="B21" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="G21" s="26"/>
-      <c r="H21" s="27"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="55" t="s">
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="52"/>
+      <c r="B23" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" s="55" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22" s="20"/>
-      <c r="F22" s="55" t="s">
-        <v>37</v>
-      </c>
-      <c r="G22" s="20"/>
-      <c r="H22" s="21" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="22"/>
-      <c r="B23" s="56" t="s">
+      <c r="C23" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="45" t="s">
+      <c r="D23" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="56" t="s">
+      <c r="E23" s="2"/>
+      <c r="F23" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="56" t="s">
+      <c r="G23" s="2"/>
+      <c r="H23" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="23" t="s">
-        <v>42</v>
-      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="22"/>
+      <c r="A24" s="52"/>
       <c r="B24" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="57" t="s">
-        <v>37</v>
+      <c r="C24" s="47" t="s">
+        <v>36</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E24" s="2"/>
-      <c r="F24" s="47" t="s">
-        <v>37</v>
+      <c r="F24" s="37" t="s">
+        <v>36</v>
       </c>
       <c r="G24" s="2"/>
-      <c r="H24" s="23"/>
+      <c r="H24" s="17"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="22"/>
+      <c r="A25" s="52"/>
       <c r="B25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="56" t="s">
+      <c r="D25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="45" t="s">
+      <c r="G25" s="2"/>
+      <c r="H25" s="17"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="52"/>
+      <c r="B26" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="23"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="22"/>
-      <c r="B26" s="52" t="s">
+      <c r="C26" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="17"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="52"/>
+      <c r="B27" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="57" t="s">
-        <v>37</v>
-      </c>
-      <c r="D26" s="47" t="s">
-        <v>37</v>
-      </c>
-      <c r="E26" s="2"/>
-      <c r="F26" s="47" t="s">
-        <v>37</v>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="23"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="22"/>
-      <c r="B27" s="53" t="s">
+      <c r="C27" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="56" t="s">
+      <c r="D27" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="D27" s="45" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27" s="2"/>
-      <c r="F27" s="45" t="s">
+      <c r="G27" s="2"/>
+      <c r="H27" s="17"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="52"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" s="35"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="17"/>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="53"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="G27" s="2"/>
-      <c r="H27" s="23"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="22"/>
-      <c r="B28" s="53"/>
-      <c r="C28" s="47" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" s="45"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="23"/>
-    </row>
-    <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="24"/>
-      <c r="B29" s="54"/>
-      <c r="C29" s="46" t="s">
+      <c r="D29" s="36"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="20"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="D29" s="46"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="27"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="18" t="s">
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="16"/>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="53"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="20"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="H30" s="21"/>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="24"/>
-      <c r="B31" s="26"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="H31" s="27"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
+      <c r="B32" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="52"/>
+      <c r="B33" s="35" t="s">
         <v>52</v>
-      </c>
-      <c r="B32" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="G32" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="H32" s="38" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="22"/>
-      <c r="B33" s="45" t="s">
-        <v>53</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G33" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="G33" s="45" t="s">
+      <c r="H33" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="52"/>
+      <c r="B34" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="H33" s="41" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="22"/>
-      <c r="B34" s="48" t="s">
+      <c r="C34" s="2"/>
+      <c r="D34" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="E34" s="2"/>
-      <c r="F34" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="G34" s="47" t="s">
+      <c r="H34" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="H34" s="40" t="s">
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="52"/>
+      <c r="B35" s="41" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="22"/>
-      <c r="B35" s="51" t="s">
+      <c r="C35" s="2"/>
+      <c r="D35" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="45" t="s">
+      <c r="E35" s="2"/>
+      <c r="F35" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="G35" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="E35" s="2"/>
-      <c r="F35" s="45" t="s">
-        <v>53</v>
-      </c>
-      <c r="G35" s="45" t="s">
+      <c r="H35" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="H35" s="41" t="s">
-        <v>63</v>
-      </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="22"/>
-      <c r="B36" s="51"/>
+      <c r="A36" s="52"/>
+      <c r="B36" s="41"/>
       <c r="C36" s="2"/>
-      <c r="D36" s="47" t="s">
-        <v>58</v>
+      <c r="D36" s="37" t="s">
+        <v>57</v>
       </c>
       <c r="E36" s="2"/>
-      <c r="F36" s="45"/>
+      <c r="F36" s="35"/>
       <c r="G36" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H36" s="32" t="s">
+      <c r="H36" s="22" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="22"/>
-      <c r="B37" s="51"/>
+      <c r="A37" s="52"/>
+      <c r="B37" s="41"/>
       <c r="C37" s="2"/>
-      <c r="D37" s="45" t="s">
+      <c r="D37" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H37" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="E37" s="2"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H37" s="23" t="s">
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="52"/>
+      <c r="B38" s="41"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="17"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="52"/>
+      <c r="B39" s="41"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="35" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="22"/>
-      <c r="B38" s="51"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="E38" s="2"/>
-      <c r="F38" s="45"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="23"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="22"/>
-      <c r="B39" s="51"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="45" t="s">
+      <c r="E39" s="2"/>
+      <c r="F39" s="35"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="17"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="52"/>
+      <c r="B40" s="41"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="17"/>
+    </row>
+    <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="53"/>
+      <c r="B41" s="39"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="E39" s="2"/>
-      <c r="F39" s="45"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="23"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="22"/>
-      <c r="B40" s="51"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="E40" s="2"/>
-      <c r="F40" s="45"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="23"/>
-    </row>
-    <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="24"/>
-      <c r="B41" s="49"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="46" t="s">
+      <c r="E41" s="19"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="20"/>
+    </row>
+    <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="E41" s="26"/>
-      <c r="F41" s="46"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="27"/>
-    </row>
-    <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="28" t="s">
+      <c r="B42" s="48"/>
+      <c r="C42" s="49"/>
+      <c r="D42" s="49"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="49"/>
+      <c r="G42" s="49"/>
+      <c r="H42" s="50"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="29"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="31"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="18" t="s">
+      <c r="B43" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="C43" s="15"/>
+      <c r="D43" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="E43" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="F43" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="G43" s="15"/>
+      <c r="H43" s="16"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="52"/>
+      <c r="B44" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="B43" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="C43" s="20"/>
-      <c r="D43" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="E43" s="55" t="s">
-        <v>37</v>
-      </c>
-      <c r="F43" s="55" t="s">
-        <v>37</v>
-      </c>
-      <c r="G43" s="20"/>
-      <c r="H43" s="21"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="22"/>
-      <c r="B44" s="45" t="s">
+      <c r="C44" s="2"/>
+      <c r="D44" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="C44" s="2"/>
-      <c r="D44" s="45" t="s">
+      <c r="E44" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="F44" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="E44" s="56" t="s">
-        <v>49</v>
-      </c>
-      <c r="F44" s="56" t="s">
-        <v>72</v>
-      </c>
       <c r="G44" s="2"/>
-      <c r="H44" s="23"/>
+      <c r="H44" s="17"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="22"/>
-      <c r="B45" s="45"/>
+      <c r="A45" s="52"/>
+      <c r="B45" s="35"/>
       <c r="C45" s="2"/>
-      <c r="D45" s="57" t="s">
-        <v>37</v>
-      </c>
-      <c r="E45" s="47" t="s">
-        <v>37</v>
+      <c r="D45" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="E45" s="37" t="s">
+        <v>36</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G45" s="2"/>
-      <c r="H45" s="23"/>
+      <c r="H45" s="17"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="22"/>
-      <c r="B46" s="45"/>
+      <c r="A46" s="52"/>
+      <c r="B46" s="35"/>
       <c r="C46" s="2"/>
-      <c r="D46" s="56" t="s">
+      <c r="D46" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="E46" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="E46" s="45" t="s">
+      <c r="F46" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="G46" s="2"/>
-      <c r="H46" s="23"/>
+      <c r="H46" s="17"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="22"/>
-      <c r="B47" s="45"/>
+      <c r="A47" s="52"/>
+      <c r="B47" s="35"/>
       <c r="C47" s="2"/>
-      <c r="D47" s="47" t="s">
-        <v>37</v>
-      </c>
-      <c r="E47" s="45"/>
+      <c r="D47" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E47" s="35"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
-      <c r="H47" s="23"/>
+      <c r="H47" s="17"/>
     </row>
     <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="24"/>
-      <c r="B48" s="46"/>
-      <c r="C48" s="26"/>
-      <c r="D48" s="46" t="s">
-        <v>76</v>
-      </c>
-      <c r="E48" s="46"/>
-      <c r="F48" s="26"/>
-      <c r="G48" s="26"/>
-      <c r="H48" s="27"/>
+      <c r="A48" s="53"/>
+      <c r="B48" s="36"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="E48" s="36"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="20"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="B49" s="20"/>
-      <c r="C49" s="20"/>
-      <c r="D49" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="E49" s="20"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="H49" s="21"/>
+      <c r="A49" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="B49" s="15"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49" s="15"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="H49" s="16"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="22"/>
+      <c r="A50" s="52"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
-      <c r="D50" s="45" t="s">
-        <v>20</v>
+      <c r="D50" s="35" t="s">
+        <v>19</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
-      <c r="G50" s="45" t="s">
-        <v>21</v>
-      </c>
-      <c r="H50" s="23"/>
+      <c r="G50" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="H50" s="17"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="22"/>
+      <c r="A51" s="52"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
-      <c r="D51" s="45"/>
+      <c r="D51" s="35"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
-      <c r="G51" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="H51" s="23"/>
+      <c r="G51" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="H51" s="17"/>
     </row>
     <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="24"/>
-      <c r="B52" s="26"/>
-      <c r="C52" s="26"/>
-      <c r="D52" s="46"/>
-      <c r="E52" s="26"/>
-      <c r="F52" s="26"/>
-      <c r="G52" s="46" t="s">
+      <c r="A52" s="53"/>
+      <c r="B52" s="19"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="36"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="H52" s="27"/>
+      <c r="H52" s="20"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="B53" s="20"/>
-      <c r="C53" s="20"/>
-      <c r="D53" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="E53" s="20"/>
-      <c r="F53" s="20"/>
-      <c r="G53" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="H53" s="21"/>
+      <c r="A53" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="B53" s="15"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" s="15"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="H53" s="16"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="22"/>
+      <c r="A54" s="52"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
-      <c r="D54" s="45" t="s">
-        <v>20</v>
+      <c r="D54" s="35" t="s">
+        <v>19</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
-      <c r="G54" s="45" t="s">
-        <v>21</v>
-      </c>
-      <c r="H54" s="23"/>
+      <c r="G54" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="H54" s="17"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="22"/>
+      <c r="A55" s="52"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
-      <c r="D55" s="45"/>
+      <c r="D55" s="35"/>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
-      <c r="G55" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="H55" s="23"/>
+      <c r="G55" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="H55" s="17"/>
     </row>
     <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="24"/>
-      <c r="B56" s="26"/>
-      <c r="C56" s="26"/>
-      <c r="D56" s="46"/>
-      <c r="E56" s="26"/>
-      <c r="F56" s="26"/>
-      <c r="G56" s="46" t="s">
+      <c r="A56" s="53"/>
+      <c r="B56" s="19"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="36"/>
+      <c r="E56" s="19"/>
+      <c r="F56" s="19"/>
+      <c r="G56" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="H56" s="27"/>
+      <c r="H56" s="20"/>
     </row>
     <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="28" t="s">
+      <c r="A57" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B57" s="48"/>
+      <c r="C57" s="49"/>
+      <c r="D57" s="49"/>
+      <c r="E57" s="49"/>
+      <c r="F57" s="49"/>
+      <c r="G57" s="49"/>
+      <c r="H57" s="50"/>
+    </row>
+    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="B57" s="29"/>
-      <c r="C57" s="30"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="30"/>
-      <c r="F57" s="30"/>
-      <c r="G57" s="30"/>
-      <c r="H57" s="31"/>
-    </row>
-    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="28" t="s">
+      <c r="B58" s="48"/>
+      <c r="C58" s="49"/>
+      <c r="D58" s="49"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49"/>
+      <c r="G58" s="49"/>
+      <c r="H58" s="50"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="B58" s="29"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
-      <c r="G58" s="30"/>
-      <c r="H58" s="31"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="18" t="s">
+      <c r="B59" s="15"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" s="15"/>
+      <c r="H59" s="16"/>
+    </row>
+    <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="53"/>
+      <c r="B60" s="19"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="19"/>
+      <c r="E60" s="19"/>
+      <c r="F60" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="G60" s="19"/>
+      <c r="H60" s="20"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="B59" s="20"/>
-      <c r="C59" s="20"/>
-      <c r="D59" s="20"/>
-      <c r="E59" s="20"/>
-      <c r="F59" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="G59" s="20"/>
-      <c r="H59" s="21"/>
-    </row>
-    <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="24"/>
-      <c r="B60" s="26"/>
-      <c r="C60" s="26"/>
-      <c r="D60" s="26"/>
-      <c r="E60" s="26"/>
-      <c r="F60" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="G60" s="26"/>
-      <c r="H60" s="27"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="18" t="s">
+      <c r="B61" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="C61" s="15"/>
+      <c r="D61" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="E61" s="15"/>
+      <c r="F61" s="15"/>
+      <c r="G61" s="15"/>
+      <c r="H61" s="16"/>
+    </row>
+    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="53"/>
+      <c r="B62" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="C62" s="19"/>
+      <c r="D62" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="E62" s="19"/>
+      <c r="F62" s="19"/>
+      <c r="G62" s="19"/>
+      <c r="H62" s="20"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="B61" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="C61" s="20"/>
-      <c r="D61" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="E61" s="20"/>
-      <c r="F61" s="20"/>
-      <c r="G61" s="20"/>
-      <c r="H61" s="21"/>
-    </row>
-    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="24"/>
-      <c r="B62" s="49" t="s">
-        <v>60</v>
-      </c>
-      <c r="C62" s="26"/>
-      <c r="D62" s="49" t="s">
-        <v>60</v>
-      </c>
-      <c r="E62" s="26"/>
-      <c r="F62" s="26"/>
-      <c r="G62" s="26"/>
-      <c r="H62" s="27"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="B63" s="20"/>
-      <c r="C63" s="20"/>
-      <c r="D63" s="20"/>
-      <c r="E63" s="20"/>
-      <c r="F63" s="20"/>
-      <c r="G63" s="20"/>
-      <c r="H63" s="38" t="s">
+      <c r="B63" s="15"/>
+      <c r="C63" s="15"/>
+      <c r="D63" s="15"/>
+      <c r="E63" s="15"/>
+      <c r="F63" s="15"/>
+      <c r="G63" s="15"/>
+      <c r="H63" s="28" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="22"/>
+      <c r="A64" s="52"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
-      <c r="H64" s="41" t="s">
-        <v>45</v>
+      <c r="H64" s="31" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="22"/>
+      <c r="A65" s="52"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
-      <c r="H65" s="32" t="s">
+      <c r="H65" s="22" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="22"/>
+      <c r="A66" s="52"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
-      <c r="H66" s="23" t="s">
-        <v>85</v>
+      <c r="H66" s="17" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="22"/>
+      <c r="A67" s="52"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
-      <c r="H67" s="40" t="s">
+      <c r="H67" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="24"/>
-      <c r="B68" s="26"/>
-      <c r="C68" s="26"/>
-      <c r="D68" s="26"/>
-      <c r="E68" s="26"/>
-      <c r="F68" s="26"/>
-      <c r="G68" s="26"/>
-      <c r="H68" s="39" t="s">
+      <c r="A68" s="53"/>
+      <c r="B68" s="19"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="19"/>
+      <c r="E68" s="19"/>
+      <c r="F68" s="19"/>
+      <c r="G68" s="19"/>
+      <c r="H68" s="29" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="51" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="B69" s="20"/>
-      <c r="C69" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="D69" s="20"/>
-      <c r="E69" s="20"/>
-      <c r="F69" s="20"/>
-      <c r="G69" s="20"/>
-      <c r="H69" s="21"/>
+      <c r="B69" s="15"/>
+      <c r="C69" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="D69" s="15"/>
+      <c r="E69" s="15"/>
+      <c r="F69" s="15"/>
+      <c r="G69" s="15"/>
+      <c r="H69" s="16"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="22"/>
+      <c r="A70" s="52"/>
       <c r="B70" s="2"/>
-      <c r="C70" s="45" t="s">
-        <v>53</v>
+      <c r="C70" s="35" t="s">
+        <v>52</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
-      <c r="H70" s="23"/>
+      <c r="H70" s="17"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="22"/>
+      <c r="A71" s="52"/>
       <c r="B71" s="2"/>
-      <c r="C71" s="48" t="s">
-        <v>57</v>
+      <c r="C71" s="38" t="s">
+        <v>56</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
-      <c r="H71" s="23"/>
+      <c r="H71" s="17"/>
     </row>
     <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="24"/>
-      <c r="B72" s="26"/>
-      <c r="C72" s="49" t="s">
-        <v>60</v>
-      </c>
-      <c r="D72" s="26"/>
-      <c r="E72" s="26"/>
-      <c r="F72" s="26"/>
-      <c r="G72" s="26"/>
-      <c r="H72" s="27"/>
+      <c r="A72" s="53"/>
+      <c r="B72" s="19"/>
+      <c r="C72" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="D72" s="19"/>
+      <c r="E72" s="19"/>
+      <c r="F72" s="19"/>
+      <c r="G72" s="19"/>
+      <c r="H72" s="20"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="18" t="s">
+      <c r="A73" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="B73" s="15"/>
+      <c r="C73" s="15"/>
+      <c r="D73" s="15"/>
+      <c r="E73" s="15"/>
+      <c r="F73" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" s="15"/>
+      <c r="H73" s="28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="53"/>
+      <c r="B74" s="19"/>
+      <c r="C74" s="19"/>
+      <c r="D74" s="19"/>
+      <c r="E74" s="19"/>
+      <c r="F74" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="G74" s="19"/>
+      <c r="H74" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="B73" s="20"/>
-      <c r="C73" s="20"/>
-      <c r="D73" s="20"/>
-      <c r="E73" s="20"/>
-      <c r="F73" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="G73" s="20"/>
-      <c r="H73" s="38" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="24"/>
-      <c r="B74" s="26"/>
-      <c r="C74" s="26"/>
-      <c r="D74" s="26"/>
-      <c r="E74" s="26"/>
-      <c r="F74" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="G74" s="26"/>
-      <c r="H74" s="39" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="18" t="s">
+      <c r="B75" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D75" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="B75" s="20" t="s">
+      <c r="E75" s="15"/>
+      <c r="F75" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C75" s="20" t="s">
+      <c r="G75" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="H75" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D75" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="G75" s="44" t="s">
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="52"/>
+      <c r="B76" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="H75" s="21" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="22"/>
-      <c r="B76" s="2" t="s">
+      <c r="C76" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D76" s="24" t="s">
         <v>92</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D76" s="34" t="s">
-        <v>93</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G76" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="G76" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="H76" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="H76" s="23" t="s">
-        <v>95</v>
-      </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="22"/>
-      <c r="B77" s="33" t="s">
-        <v>90</v>
+      <c r="A77" s="52"/>
+      <c r="B77" s="23" t="s">
+        <v>89</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" s="3" t="s">
@@ -6400,26 +6397,26 @@
       <c r="G77" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H77" s="23"/>
+      <c r="H77" s="17"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="22"/>
-      <c r="B78" s="34" t="s">
-        <v>96</v>
+      <c r="A78" s="52"/>
+      <c r="B78" s="24" t="s">
+        <v>95</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
       <c r="G78" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H78" s="23"/>
+        <v>96</v>
+      </c>
+      <c r="H78" s="17"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="22"/>
+      <c r="A79" s="52"/>
       <c r="B79" s="3" t="s">
         <v>12</v>
       </c>
@@ -6428,48 +6425,48 @@
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
-      <c r="H79" s="23"/>
+      <c r="H79" s="17"/>
     </row>
     <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="24"/>
-      <c r="B80" s="26" t="s">
+      <c r="A80" s="53"/>
+      <c r="B80" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C80" s="19"/>
+      <c r="D80" s="19"/>
+      <c r="E80" s="19"/>
+      <c r="F80" s="19"/>
+      <c r="G80" s="19"/>
+      <c r="H80" s="20"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="C80" s="26"/>
-      <c r="D80" s="26"/>
-      <c r="E80" s="26"/>
-      <c r="F80" s="26"/>
-      <c r="G80" s="26"/>
-      <c r="H80" s="27"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="B81" s="20"/>
-      <c r="C81" s="20"/>
-      <c r="D81" s="20"/>
-      <c r="E81" s="20"/>
-      <c r="F81" s="20"/>
-      <c r="G81" s="36" t="s">
+      <c r="B81" s="15"/>
+      <c r="C81" s="15"/>
+      <c r="D81" s="15"/>
+      <c r="E81" s="15"/>
+      <c r="F81" s="15"/>
+      <c r="G81" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="H81" s="21"/>
+      <c r="H81" s="16"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="22"/>
+      <c r="A82" s="52"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
-      <c r="G82" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="H82" s="23"/>
+      <c r="G82" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="H82" s="17"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="22"/>
+      <c r="A83" s="52"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
@@ -6478,48 +6475,57 @@
       <c r="G83" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H83" s="23"/>
+      <c r="H83" s="17"/>
     </row>
     <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="24"/>
-      <c r="B84" s="26"/>
-      <c r="C84" s="26"/>
-      <c r="D84" s="26"/>
-      <c r="E84" s="26"/>
-      <c r="F84" s="26"/>
-      <c r="G84" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="H84" s="27"/>
+      <c r="A84" s="53"/>
+      <c r="B84" s="19"/>
+      <c r="C84" s="19"/>
+      <c r="D84" s="19"/>
+      <c r="E84" s="19"/>
+      <c r="F84" s="19"/>
+      <c r="G84" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="H84" s="20"/>
     </row>
     <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="B85" s="29"/>
-      <c r="C85" s="30"/>
-      <c r="D85" s="30"/>
-      <c r="E85" s="30"/>
-      <c r="F85" s="30"/>
-      <c r="G85" s="30"/>
-      <c r="H85" s="31"/>
+      <c r="A85" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B85" s="48"/>
+      <c r="C85" s="49"/>
+      <c r="D85" s="49"/>
+      <c r="E85" s="49"/>
+      <c r="F85" s="49"/>
+      <c r="G85" s="49"/>
+      <c r="H85" s="50"/>
     </row>
     <row r="86" spans="1:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="17"/>
-      <c r="C86" s="17"/>
-      <c r="D86" s="17"/>
-      <c r="E86" s="17"/>
-      <c r="F86" s="17"/>
-      <c r="G86" s="17"/>
-      <c r="H86" s="17"/>
+      <c r="B86" s="54"/>
+      <c r="C86" s="54"/>
+      <c r="D86" s="54"/>
+      <c r="E86" s="54"/>
+      <c r="F86" s="54"/>
+      <c r="G86" s="54"/>
+      <c r="H86" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B58:H58"/>
-    <mergeCell ref="B57:H57"/>
-    <mergeCell ref="B85:H85"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A29"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="A49:A52"/>
+    <mergeCell ref="A53:A56"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A41"/>
+    <mergeCell ref="A43:A48"/>
     <mergeCell ref="A81:A84"/>
     <mergeCell ref="B86:H86"/>
     <mergeCell ref="A61:A62"/>
@@ -6527,20 +6533,11 @@
     <mergeCell ref="A69:A72"/>
     <mergeCell ref="A73:A74"/>
     <mergeCell ref="A75:A80"/>
-    <mergeCell ref="A49:A52"/>
-    <mergeCell ref="A53:A56"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A41"/>
-    <mergeCell ref="A43:A48"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A29"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B57:H57"/>
+    <mergeCell ref="B85:H85"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="36" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -6559,36 +6556,36 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
+      <c r="B4" s="56" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
+      <c r="B5" s="57" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>108</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -6610,7 +6607,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="8">
         <v>0</v>
@@ -6627,7 +6624,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9" s="8">
         <v>0</v>
@@ -6644,7 +6641,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10" s="8">
         <v>0</v>
@@ -6661,7 +6658,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" s="8">
         <v>0</v>
@@ -6678,7 +6675,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="8">
         <v>0</v>
@@ -6695,7 +6692,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="8">
         <v>0</v>
@@ -6712,7 +6709,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" s="8">
         <v>0</v>
@@ -6729,7 +6726,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B15" s="8">
         <v>0</v>
@@ -6746,7 +6743,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B16" s="8">
         <v>0</v>
@@ -6763,7 +6760,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B17" s="8">
         <v>0</v>
@@ -6780,7 +6777,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B18" s="8">
         <v>0</v>
@@ -6797,7 +6794,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B19" s="8">
         <v>0</v>
@@ -6814,7 +6811,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B20" s="8">
         <v>0</v>
@@ -6831,7 +6828,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B21" s="8">
         <v>0</v>
@@ -6848,7 +6845,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B22" s="8">
         <v>0</v>
@@ -6865,7 +6862,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B23" s="8">
         <v>0</v>
@@ -6882,7 +6879,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B24" s="8">
         <v>0</v>
@@ -6899,7 +6896,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B25" s="8">
         <v>0</v>
@@ -6916,7 +6913,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B26" s="8">
         <v>0</v>
@@ -6933,7 +6930,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B27" s="8">
         <v>0</v>
@@ -6950,7 +6947,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B28" s="8">
         <v>0</v>
@@ -6967,7 +6964,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B29" s="8">
         <v>0</v>
@@ -6984,7 +6981,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B30" s="8">
         <v>0</v>
@@ -7001,7 +6998,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B31" s="8">
         <v>0</v>
@@ -7018,7 +7015,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B32" s="8">
         <v>0</v>
@@ -7035,7 +7032,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B33" s="8">
         <v>0</v>
@@ -7085,40 +7082,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B5" s="12"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -7299,13 +7296,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4F30F61-E3F2-46DD-9CD8-16D0A72A34DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB4B8A6F-00BC-417E-A1D4-04BB394B4B21}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4C75DEE-4A4D-441F-9761-12F2D4B38289}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{033FFB67-241A-4A4A-9366-3A46F5EB6DD8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{521DF769-EBCF-4D2A-8040-E4E65BE4C0ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C03D5383-07A5-4190-A0C7-39DEE4515CEF}"/>
 </file>